--- a/Result/profitability/6263.xlsx
+++ b/Result/profitability/6263.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.82</v>
       </c>
       <c r="M2" t="n">
-        <v>1.955</v>
+        <v>2.00125</v>
       </c>
       <c r="N2" t="n">
-        <v>44.7275</v>
+        <v>44.81875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.55</v>
       </c>
       <c r="M3" t="n">
-        <v>1.765</v>
+        <v>1.7775</v>
       </c>
       <c r="N3" t="n">
-        <v>42.2075</v>
+        <v>42.27625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.78</v>
       </c>
       <c r="M4" t="n">
-        <v>1.57</v>
+        <v>1.6125</v>
       </c>
       <c r="N4" t="n">
-        <v>39.79625</v>
+        <v>39.80625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.64</v>
       </c>
       <c r="M5" t="n">
-        <v>1.3875</v>
+        <v>1.4525</v>
       </c>
       <c r="N5" t="n">
-        <v>37.4425</v>
+        <v>37.68375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.62</v>
       </c>
       <c r="M6" t="n">
-        <v>1.225</v>
+        <v>1.29625</v>
       </c>
       <c r="N6" t="n">
-        <v>35.525</v>
+        <v>35.93375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.37</v>
       </c>
       <c r="M7" t="n">
-        <v>1.0375</v>
+        <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>33.575</v>
+        <v>33.5825</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.48</v>
       </c>
       <c r="M8" t="n">
-        <v>0.795</v>
+        <v>0.8375</v>
       </c>
       <c r="N8" t="n">
-        <v>31.29875</v>
+        <v>31.2675</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.82</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6349999999999999</v>
+        <v>0.635</v>
       </c>
       <c r="N9" t="n">
         <v>28.97375</v>
@@ -1645,7 +1645,7 @@
         <v>0.38</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5800000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="N10" t="n">
         <v>29.05125</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6263</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>519</v>
+      </c>
+      <c r="D75" t="n">
+        <v>270</v>
+      </c>
+      <c r="E75" t="n">
+        <v>249</v>
+      </c>
+      <c r="F75" t="n">
+        <v>47.96</v>
+      </c>
+      <c r="G75" t="n">
+        <v>179</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>34.41%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>8</v>
+      </c>
+      <c r="J75" t="n">
+        <v>187</v>
+      </c>
+      <c r="K75" t="n">
+        <v>152</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.1575</v>
+      </c>
+      <c r="N75" t="n">
+        <v>47.16375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3399999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1619047619047618</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.005185646131507959</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.04192917662394091</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
